--- a/downloads/excel/Форма_оформления_календарного_плана_мероприятий_при_угрозе_возникновения_и_возникновении_ЧС.xlsx
+++ b/downloads/excel/Форма_оформления_календарного_плана_мероприятий_при_угрозе_возникновения_и_возникновении_ЧС.xlsx
@@ -63,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -85,21 +85,150 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,29 +598,29 @@
   <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,7 +630,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -531,416 +659,373 @@
           <t>Время выполнения</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>N п/п</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Основные меро-
-приятия</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Исполни-
-тели</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Отведен-
-ное время</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Первый день</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Сутки</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>N п/п</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Основные меро-
-приятия</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Исполни-
-тели</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Отведен-
-ное время</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Минуты</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Часы</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>Сутки</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="8" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>N п/п</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Основные меро-
-приятия</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Исполни-
-тели</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Отведен-
-ное время</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Мероприятия в режиме "повседневная деятельность"</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr"/>
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Мероприятия в режиме "повышенная готовность"</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="4" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Мероприятия в режиме "чрезвычайная ситуация"</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="inlineStr"/>
-      <c r="W12" s="3" t="inlineStr"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="4" t="n"/>
+      <c r="T12" s="13" t="n"/>
+      <c r="U12" s="13" t="n"/>
+      <c r="V12" s="13" t="n"/>
+      <c r="W12" s="13" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="H12:S12"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="H10:S10"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="H5:S5"/>
+    <mergeCell ref="E3:W3"/>
+    <mergeCell ref="A7:W7"/>
+    <mergeCell ref="H8:S8"/>
+    <mergeCell ref="A11:W11"/>
+    <mergeCell ref="E4:S4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>